--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -546,10 +546,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -698,10 +698,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -948,8 +948,8 @@
       <c r="E16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="15">
-        <v>1</v>
+      <c r="F16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -980,8 +980,8 @@
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>20</v>
@@ -989,32 +989,32 @@
       <c r="E17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>20</v>
+      <c r="F17" s="15">
+        <v>1</v>
       </c>
       <c r="G17" s="15">
         <v>2</v>
       </c>
       <c r="H17" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I17" s="15">
+        <v>1</v>
       </c>
       <c r="J17" s="15">
         <v>2</v>
       </c>
       <c r="K17" s="14">
-        <v>-100</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>21</v>
+        <v>-50</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N17" s="14">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1062,49 +1062,49 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="15">
-        <v>3</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-100</v>
+      <c r="C19" s="15">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F19" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="15">
         <v>3</v>
       </c>
       <c r="H19" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="15">
         <v>3</v>
       </c>
       <c r="K19" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L19" s="14">
+        <v>0</v>
+      </c>
+      <c r="M19" s="14">
         <v>-50</v>
       </c>
-      <c r="M19" s="14">
+      <c r="N19" s="14">
         <v>-75</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1113,7 +1113,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1122,7 +1122,7 @@
         <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="13" t="s">
         <v>20</v>
@@ -1136,49 +1136,49 @@
       <c r="M20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N20" s="13" t="s">
-        <v>21</v>
+      <c r="N20" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="18">
+      <c r="C21" s="17">
         <v>3</v>
       </c>
-      <c r="E21" s="19">
-        <v>-100</v>
-      </c>
-      <c r="F21" s="18">
-        <v>3</v>
-      </c>
-      <c r="G21" s="18">
+      <c r="D21" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="17">
         <v>5</v>
       </c>
+      <c r="G21" s="17">
+        <v>5</v>
+      </c>
       <c r="H21" s="19">
-        <v>-40</v>
-      </c>
-      <c r="I21" s="18">
-        <v>3</v>
-      </c>
-      <c r="J21" s="18">
+        <v>0</v>
+      </c>
+      <c r="I21" s="17">
+        <v>6</v>
+      </c>
+      <c r="J21" s="17">
         <v>5</v>
       </c>
       <c r="K21" s="19">
-        <v>-40</v>
+        <v>20</v>
       </c>
       <c r="L21" s="19">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M21" s="19">
-        <v>-40</v>
+        <v>20</v>
       </c>
       <c r="N21" s="19">
-        <v>-88.888888888888</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1267,8 +1267,8 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>2</v>
+      <c r="C24" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>20</v>
@@ -1434,11 +1434,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
@@ -1966,19 +1966,19 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="17">
         <v>368</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="17">
         <v>475</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="17">
         <v>187</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="17">
         <v>127</v>
       </c>
-      <c r="J46" s="18">
+      <c r="J46" s="17">
         <v>85</v>
       </c>
       <c r="K46" s="25">

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -547,9 +547,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -698,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -731,24 +728,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="29" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="28"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -770,45 +767,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="34" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="34" t="s">
+      <c r="G12" s="32"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="34" t="s">
+      <c r="J12" s="32"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="36" t="s">
         <v>16</v>
       </c>
     </row>
@@ -939,49 +936,49 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15">
+        <v>1</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
       </c>
       <c r="I16" s="15">
+        <v>2</v>
+      </c>
+      <c r="J16" s="15">
         <v>1</v>
       </c>
-      <c r="J16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>21</v>
+      <c r="K16" s="14">
+        <v>100</v>
       </c>
       <c r="L16" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.857142857142</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>1</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>20</v>
@@ -1062,49 +1059,49 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="15">
         <v>1</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>21</v>
+      <c r="E19" s="14">
+        <v>-100</v>
       </c>
       <c r="F19" s="15">
         <v>2</v>
       </c>
       <c r="G19" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I19" s="15">
         <v>2</v>
       </c>
       <c r="J19" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L19" s="14">
         <v>0</v>
       </c>
       <c r="M19" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N19" s="14">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1145,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>3</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D21" s="17">
+        <v>2</v>
+      </c>
+      <c r="E21" s="18">
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" s="17">
-        <v>5</v>
-      </c>
-      <c r="H21" s="19">
+        <v>7</v>
+      </c>
+      <c r="H21" s="18">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="I21" s="17">
+        <v>7</v>
+      </c>
+      <c r="J21" s="17">
+        <v>7</v>
+      </c>
+      <c r="K21" s="18">
         <v>0</v>
       </c>
-      <c r="I21" s="17">
-        <v>6</v>
-      </c>
-      <c r="J21" s="17">
-        <v>5</v>
-      </c>
-      <c r="K21" s="19">
-        <v>20</v>
-      </c>
-      <c r="L21" s="19">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="M21" s="19">
-        <v>20</v>
-      </c>
-      <c r="N21" s="19">
-        <v>-81.25</v>
+      <c r="L21" s="18">
+        <v>-12.5</v>
+      </c>
+      <c r="M21" s="18">
+        <v>16.666666666666</v>
+      </c>
+      <c r="N21" s="18">
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1279,11 +1276,11 @@
       <c r="F24" s="15">
         <v>2</v>
       </c>
-      <c r="G24" s="15">
-        <v>1</v>
-      </c>
-      <c r="H24" s="14">
-        <v>100</v>
+      <c r="G24" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I24" s="15">
         <v>2</v>
@@ -1358,8 +1355,8 @@
       <c r="E26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="15">
-        <v>1</v>
+      <c r="F26" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>20</v>
@@ -1377,10 +1374,10 @@
         <v>100</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1434,29 +1431,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="D28" s="15">
         <v>1</v>
       </c>
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="15">
         <v>1</v>
       </c>
       <c r="J28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="13" t="s">
         <v>21</v>
@@ -1595,19 +1592,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1654,93 +1651,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="K37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="22" t="s">
+      <c r="I38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="22">
         <v>2025</v>
       </c>
-      <c r="K38" s="22" t="s">
+      <c r="K38" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="M38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="22" t="s">
+      <c r="N38" s="21" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1981,51 +1978,51 @@
       <c r="J46" s="17">
         <v>85</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="24">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="25">
+      <c r="L46" s="24">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="25">
+      <c r="M46" s="24">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="24">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="25" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="25" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="25" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="25" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="25" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2033,7 +2030,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="27" t="s">
+      <c r="K57" s="26" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +544,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -728,24 +731,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="28" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="27"/>
+      <c r="N7" s="28"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -767,45 +770,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="33" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="33" t="s">
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="33" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="33" t="s">
+      <c r="J12" s="33"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="37" t="s">
         <v>16</v>
       </c>
     </row>
@@ -936,14 +939,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
         <v>1</v>
@@ -964,13 +967,13 @@
         <v>100</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M16" s="14">
         <v>100</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -989,11 +992,11 @@
       <c r="F17" s="15">
         <v>1</v>
       </c>
-      <c r="G17" s="15">
-        <v>2</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-50</v>
+      <c r="G17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I17" s="15">
         <v>1</v>
@@ -1062,20 +1065,20 @@
       <c r="C19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="15">
         <v>1</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F19" s="15">
-        <v>2</v>
       </c>
       <c r="G19" s="15">
         <v>4</v>
       </c>
       <c r="H19" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I19" s="15">
         <v>2</v>
@@ -1110,7 +1113,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1141,41 +1144,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17">
-        <v>1</v>
-      </c>
-      <c r="D21" s="17">
-        <v>2</v>
-      </c>
-      <c r="E21" s="18">
-        <v>-50</v>
-      </c>
-      <c r="F21" s="17">
-        <v>6</v>
-      </c>
-      <c r="G21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="18">
+        <v>4</v>
+      </c>
+      <c r="G21" s="18">
+        <v>5</v>
+      </c>
+      <c r="H21" s="19">
+        <v>-20</v>
+      </c>
+      <c r="I21" s="18">
         <v>7</v>
       </c>
-      <c r="H21" s="18">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="J21" s="18">
         <v>7</v>
       </c>
-      <c r="J21" s="17">
-        <v>7</v>
-      </c>
-      <c r="K21" s="18">
+      <c r="K21" s="19">
         <v>0</v>
       </c>
-      <c r="L21" s="18">
-        <v>-12.5</v>
-      </c>
-      <c r="M21" s="18">
+      <c r="L21" s="19">
+        <v>-46.153846153846</v>
+      </c>
+      <c r="M21" s="19">
         <v>16.666666666666</v>
       </c>
-      <c r="N21" s="18">
-        <v>-80</v>
+      <c r="N21" s="19">
+        <v>-82.051282051282</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1291,8 +1294,8 @@
       <c r="K24" s="14">
         <v>100</v>
       </c>
-      <c r="L24" s="13" t="s">
-        <v>21</v>
+      <c r="L24" s="14">
+        <v>100</v>
       </c>
       <c r="M24" s="14">
         <v>100</v>
@@ -1349,29 +1352,29 @@
       <c r="C26" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+      <c r="D26" s="15">
+        <v>1</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-100</v>
       </c>
       <c r="F26" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>21</v>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="14">
+        <v>-100</v>
       </c>
       <c r="I26" s="15">
         <v>2</v>
       </c>
       <c r="J26" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14">
         <v>-33.333333333333</v>
@@ -1431,11 +1434,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>20</v>
@@ -1592,19 +1595,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1651,93 +1654,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="31"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="32"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="20" t="s">
+      <c r="J37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="21" t="s">
+      <c r="L37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="21" t="s">
+      <c r="M37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="21" t="s">
+      <c r="N37" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="23">
         <v>2025</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="21" t="s">
+      <c r="M38" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="21" t="s">
+      <c r="N38" s="22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1963,66 +1966,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="18">
         <v>368</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="18">
         <v>475</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="18">
         <v>187</v>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="18">
         <v>127</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="18">
         <v>85</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="25">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L46" s="25">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="24">
+      <c r="M46" s="25">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="24">
+      <c r="N46" s="25">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="26" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="26" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="26" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2030,7 +2033,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="26" t="s">
+      <c r="K57" s="27" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -967,10 +967,10 @@
         <v>100</v>
       </c>
       <c r="L16" s="14">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="M16" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="14">
         <v>-90</v>
@@ -983,29 +983,29 @@
       <c r="C17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14">
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>21</v>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
       </c>
       <c r="I17" s="15">
         <v>1</v>
       </c>
       <c r="J17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L17" s="14">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>21</v>
       </c>
       <c r="N17" s="14">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1065,38 +1065,38 @@
       <c r="C19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>21</v>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14">
+        <v>-100</v>
       </c>
       <c r="F19" s="15">
         <v>1</v>
       </c>
       <c r="G19" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I19" s="15">
         <v>2</v>
       </c>
       <c r="J19" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L19" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="14">
         <v>-60</v>
       </c>
       <c r="N19" s="14">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1147,38 +1147,38 @@
       <c r="C21" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>21</v>
+      <c r="D21" s="18">
+        <v>2</v>
+      </c>
+      <c r="E21" s="19">
+        <v>-100</v>
       </c>
       <c r="F21" s="18">
         <v>4</v>
       </c>
       <c r="G21" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21" s="19">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I21" s="18">
         <v>7</v>
       </c>
       <c r="J21" s="18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K21" s="19">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L21" s="19">
-        <v>-46.153846153846</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M21" s="19">
-        <v>16.666666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="N21" s="19">
-        <v>-82.051282051282</v>
+        <v>-82.926829268292</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1276,8 +1276,8 @@
       <c r="E24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="15">
-        <v>2</v>
+      <c r="F24" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>20</v>
@@ -1362,7 +1362,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="14">
         <v>-100</v>
@@ -1371,16 +1371,16 @@
         <v>2</v>
       </c>
       <c r="J26" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L26" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1444,7 +1444,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
         <v>-100</v>
@@ -1458,8 +1458,8 @@
       <c r="K28" s="14">
         <v>-50</v>
       </c>
-      <c r="L28" s="13" t="s">
-        <v>21</v>
+      <c r="L28" s="14">
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,9 +544,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -698,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -731,24 +728,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="29" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="28"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -770,45 +767,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="34" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="34" t="s">
+      <c r="G12" s="32"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="34" t="s">
+      <c r="J12" s="32"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="36" t="s">
         <v>16</v>
       </c>
     </row>
@@ -939,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
+        <v>3</v>
+      </c>
+      <c r="J16" s="15">
         <v>2</v>
       </c>
-      <c r="J16" s="15">
-        <v>1</v>
-      </c>
       <c r="K16" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L16" s="14">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="M16" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="14">
-        <v>-90</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -989,23 +986,23 @@
       <c r="E17" s="14">
         <v>-100</v>
       </c>
-      <c r="F17" s="15">
-        <v>1</v>
+      <c r="F17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I17" s="15">
         <v>1</v>
       </c>
       <c r="J17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L17" s="14">
         <v>0</v>
@@ -1071,29 +1068,29 @@
       <c r="E19" s="14">
         <v>-100</v>
       </c>
-      <c r="F19" s="15">
-        <v>1</v>
+      <c r="F19" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G19" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I19" s="15">
         <v>2</v>
       </c>
       <c r="J19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K19" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M19" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N19" s="14">
         <v>-80</v>
@@ -1112,8 +1109,8 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="15">
-        <v>1</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1144,41 +1141,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="18">
+      <c r="C21" s="17">
+        <v>1</v>
+      </c>
+      <c r="D21" s="17">
+        <v>3</v>
+      </c>
+      <c r="E21" s="18">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F21" s="17">
         <v>2</v>
       </c>
-      <c r="E21" s="19">
-        <v>-100</v>
-      </c>
-      <c r="F21" s="18">
-        <v>4</v>
-      </c>
-      <c r="G21" s="18">
-        <v>4</v>
-      </c>
-      <c r="H21" s="19">
-        <v>0</v>
-      </c>
-      <c r="I21" s="18">
+      <c r="G21" s="17">
         <v>7</v>
       </c>
-      <c r="J21" s="18">
-        <v>9</v>
-      </c>
-      <c r="K21" s="19">
-        <v>-22.222222222222</v>
-      </c>
-      <c r="L21" s="19">
-        <v>-53.333333333333</v>
-      </c>
-      <c r="M21" s="19">
-        <v>-12.5</v>
-      </c>
-      <c r="N21" s="19">
-        <v>-82.926829268292</v>
+      <c r="H21" s="18">
+        <v>-71.428571428571</v>
+      </c>
+      <c r="I21" s="17">
+        <v>8</v>
+      </c>
+      <c r="J21" s="17">
+        <v>12</v>
+      </c>
+      <c r="K21" s="18">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L21" s="18">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="M21" s="18">
+        <v>-20</v>
+      </c>
+      <c r="N21" s="18">
+        <v>-80.952380952380</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1295,7 +1292,7 @@
         <v>100</v>
       </c>
       <c r="L24" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="14">
         <v>100</v>
@@ -1352,11 +1349,11 @@
       <c r="C26" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="15">
-        <v>1</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-100</v>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="13" t="s">
         <v>20</v>
@@ -1377,7 +1374,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L26" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M26" s="14">
         <v>-60</v>
@@ -1595,19 +1592,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1654,93 +1651,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="K37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="22" t="s">
+      <c r="I38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="22">
         <v>2025</v>
       </c>
-      <c r="K38" s="22" t="s">
+      <c r="K38" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="M38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="22" t="s">
+      <c r="N38" s="21" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1966,66 +1963,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="17">
         <v>368</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="17">
         <v>475</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="17">
         <v>187</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="17">
         <v>127</v>
       </c>
-      <c r="J46" s="18">
+      <c r="J46" s="17">
         <v>85</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="24">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="25">
+      <c r="L46" s="24">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="25">
+      <c r="M46" s="24">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="24">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="25" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="25" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="25" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="25" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="25" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2033,7 +2030,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="27" t="s">
+      <c r="K57" s="26" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +544,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -695,7 +698,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -728,24 +731,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="28" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="27"/>
+      <c r="N7" s="28"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -767,45 +770,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="33" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="33" t="s">
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="33" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="33" t="s">
+      <c r="J12" s="33"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="37" t="s">
         <v>16</v>
       </c>
     </row>
@@ -936,20 +939,20 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
+      <c r="G16" s="15">
         <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
-        <v>2</v>
-      </c>
-      <c r="G16" s="15">
-        <v>2</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
@@ -970,7 +973,7 @@
         <v>-25</v>
       </c>
       <c r="N16" s="14">
-        <v>-85</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -980,11 +983,11 @@
       <c r="C17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="15">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-100</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>20</v>
@@ -1063,7 +1066,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
         <v>-100</v>
@@ -1072,7 +1075,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" s="14">
         <v>-100</v>
@@ -1081,19 +1084,19 @@
         <v>2</v>
       </c>
       <c r="J19" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K19" s="14">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="L19" s="14">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M19" s="14">
         <v>-66.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1134,48 +1137,48 @@
         <v>21</v>
       </c>
       <c r="N20" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="18">
+        <v>3</v>
+      </c>
+      <c r="E21" s="19">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="18">
         <v>1</v>
       </c>
-      <c r="D21" s="17">
-        <v>3</v>
-      </c>
-      <c r="E21" s="18">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F21" s="17">
-        <v>2</v>
-      </c>
-      <c r="G21" s="17">
-        <v>7</v>
-      </c>
-      <c r="H21" s="18">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="G21" s="18">
         <v>8</v>
       </c>
-      <c r="J21" s="17">
-        <v>12</v>
-      </c>
-      <c r="K21" s="18">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L21" s="18">
-        <v>-55.555555555555</v>
-      </c>
-      <c r="M21" s="18">
+      <c r="H21" s="19">
+        <v>-87.5</v>
+      </c>
+      <c r="I21" s="18">
+        <v>8</v>
+      </c>
+      <c r="J21" s="18">
+        <v>15</v>
+      </c>
+      <c r="K21" s="19">
+        <v>-46.666666666666</v>
+      </c>
+      <c r="L21" s="19">
+        <v>-61.904761904761</v>
+      </c>
+      <c r="M21" s="19">
         <v>-20</v>
       </c>
-      <c r="N21" s="18">
-        <v>-80.952380952380</v>
+      <c r="N21" s="19">
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1264,8 +1267,8 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>20</v>
+      <c r="C24" s="15">
+        <v>1</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>20</v>
@@ -1273,8 +1276,8 @@
       <c r="E24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>20</v>
+      <c r="F24" s="15">
+        <v>1</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>20</v>
@@ -1283,19 +1286,19 @@
         <v>21</v>
       </c>
       <c r="I24" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="15">
         <v>1</v>
       </c>
       <c r="K24" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L24" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M24" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1346,8 +1349,8 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>20</v>
+      <c r="C26" s="15">
+        <v>1</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>20</v>
@@ -1355,29 +1358,29 @@
       <c r="E26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>20</v>
+      <c r="F26" s="15">
+        <v>1</v>
       </c>
       <c r="G26" s="15">
         <v>2</v>
       </c>
       <c r="H26" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I26" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="15">
         <v>3</v>
       </c>
       <c r="K26" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M26" s="14">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1431,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1437,26 +1440,26 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="F28" s="15">
         <v>1</v>
       </c>
-      <c r="H28" s="14">
-        <v>-100</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="15">
         <v>2</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1592,19 +1595,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1651,93 +1654,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="31"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="32"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="20" t="s">
+      <c r="J37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="21" t="s">
+      <c r="L37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="21" t="s">
+      <c r="M37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="21" t="s">
+      <c r="N37" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="23">
         <v>2025</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="21" t="s">
+      <c r="M38" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="21" t="s">
+      <c r="N38" s="22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1963,66 +1966,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="18">
         <v>368</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="18">
         <v>475</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="18">
         <v>187</v>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="18">
         <v>127</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="18">
         <v>85</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="25">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L46" s="25">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="24">
+      <c r="M46" s="25">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="24">
+      <c r="N46" s="25">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="26" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="26" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="26" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2030,7 +2033,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="26" t="s">
+      <c r="K57" s="27" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -546,10 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -570,7 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -698,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -731,24 +728,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="29" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="28"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -770,45 +767,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="34" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="34" t="s">
+      <c r="G12" s="32"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="34" t="s">
+      <c r="J12" s="32"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="36" t="s">
         <v>16</v>
       </c>
     </row>
@@ -898,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -907,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -916,8 +913,8 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+      <c r="I15" s="14">
+        <v>1</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -925,14 +922,14 @@
       <c r="K15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="14">
-        <v>-100</v>
+      <c r="L15" s="15">
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N15" s="14">
-        <v>-100</v>
+      <c r="N15" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -948,31 +945,31 @@
       <c r="E16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <v>1</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <v>1</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="14">
         <v>3</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="14">
         <v>2</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="15">
         <v>50</v>
       </c>
-      <c r="L16" s="14">
-        <v>-70</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-25</v>
-      </c>
-      <c r="N16" s="14">
+      <c r="L16" s="15">
+        <v>-76.923076923076</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-40</v>
+      </c>
+      <c r="N16" s="15">
         <v>-87.5</v>
       </c>
     </row>
@@ -992,29 +989,29 @@
       <c r="F17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <v>2</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="15">
         <v>-100</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="14">
         <v>1</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="14">
         <v>4</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="15">
         <v>-75</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="15">
         <v>0</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N17" s="14">
-        <v>-87.5</v>
+      <c r="N17" s="15">
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1054,7 +1051,7 @@
       <c r="M18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1062,41 +1059,41 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="14">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>1</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="I19" s="14">
         <v>3</v>
       </c>
-      <c r="E19" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="15">
-        <v>5</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I19" s="15">
-        <v>2</v>
-      </c>
-      <c r="J19" s="15">
-        <v>9</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-77.777777777777</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-77.777777777777</v>
-      </c>
-      <c r="M19" s="14">
+      <c r="J19" s="14">
+        <v>10</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-70</v>
+      </c>
+      <c r="L19" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="N19" s="14">
-        <v>-81.818181818181</v>
+      <c r="M19" s="15">
+        <v>-50</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-80</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1121,7 +1118,7 @@
       <c r="H20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="14">
         <v>2</v>
       </c>
       <c r="J20" s="13" t="s">
@@ -1136,7 +1133,7 @@
       <c r="M20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N20" s="14">
+      <c r="N20" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1144,41 +1141,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="18">
+      <c r="C21" s="17">
+        <v>2</v>
+      </c>
+      <c r="D21" s="17">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18">
+        <v>100</v>
+      </c>
+      <c r="F21" s="17">
         <v>3</v>
       </c>
-      <c r="E21" s="19">
-        <v>-100</v>
-      </c>
-      <c r="F21" s="18">
-        <v>1</v>
-      </c>
-      <c r="G21" s="18">
-        <v>8</v>
-      </c>
-      <c r="H21" s="19">
-        <v>-87.5</v>
-      </c>
-      <c r="I21" s="18">
-        <v>8</v>
-      </c>
-      <c r="J21" s="18">
-        <v>15</v>
-      </c>
-      <c r="K21" s="19">
-        <v>-46.666666666666</v>
-      </c>
-      <c r="L21" s="19">
-        <v>-61.904761904761</v>
-      </c>
-      <c r="M21" s="19">
-        <v>-20</v>
-      </c>
-      <c r="N21" s="19">
-        <v>-83.333333333333</v>
+      <c r="G21" s="17">
+        <v>9</v>
+      </c>
+      <c r="H21" s="18">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I21" s="17">
+        <v>10</v>
+      </c>
+      <c r="J21" s="17">
+        <v>16</v>
+      </c>
+      <c r="K21" s="18">
+        <v>-37.5</v>
+      </c>
+      <c r="L21" s="18">
+        <v>-58.333333333333</v>
+      </c>
+      <c r="M21" s="18">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="N21" s="18">
+        <v>-82.142857142857</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1267,38 +1264,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
+        <v>2</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="14">
+        <v>5</v>
+      </c>
+      <c r="J24" s="14">
         <v>1</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="15">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="15">
-        <v>3</v>
-      </c>
-      <c r="J24" s="15">
-        <v>1</v>
-      </c>
-      <c r="K24" s="14">
-        <v>200</v>
-      </c>
-      <c r="L24" s="14">
-        <v>50</v>
-      </c>
-      <c r="M24" s="14">
-        <v>200</v>
+      <c r="K24" s="15">
+        <v>400</v>
+      </c>
+      <c r="L24" s="15">
+        <v>150</v>
+      </c>
+      <c r="M24" s="15">
+        <v>150</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1349,7 +1346,7 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <v>1</v>
       </c>
       <c r="D26" s="13" t="s">
@@ -1358,29 +1355,29 @@
       <c r="E26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="14">
+        <v>2</v>
+      </c>
+      <c r="G26" s="14">
         <v>1</v>
       </c>
-      <c r="G26" s="15">
-        <v>2</v>
-      </c>
-      <c r="H26" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I26" s="15">
+      <c r="H26" s="15">
+        <v>100</v>
+      </c>
+      <c r="I26" s="14">
+        <v>4</v>
+      </c>
+      <c r="J26" s="14">
         <v>3</v>
       </c>
-      <c r="J26" s="15">
-        <v>3</v>
-      </c>
-      <c r="K26" s="14">
-        <v>0</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-25</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-57.142857142857</v>
+      <c r="K26" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-20</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-42.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1399,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1408,8 +1405,8 @@
       <c r="H27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+      <c r="I27" s="14">
+        <v>1</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1417,8 +1414,8 @@
       <c r="K27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L27" s="14">
-        <v>-100</v>
+      <c r="L27" s="15">
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,34 +1428,34 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>1</v>
-      </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="14">
         <v>2</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="14">
         <v>2</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="15">
         <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
@@ -1595,19 +1592,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1654,93 +1651,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="K37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="22" t="s">
+      <c r="I38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="22">
         <v>2025</v>
       </c>
-      <c r="K38" s="22" t="s">
+      <c r="K38" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="M38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="22" t="s">
+      <c r="N38" s="21" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1748,16 +1745,16 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>3</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>2</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>1</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>1</v>
       </c>
       <c r="K39" s="13" t="s">
@@ -1777,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>10</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>11</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>4</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>3</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>3</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>0</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-25</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-72.727272727272</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-70</v>
       </c>
     </row>
@@ -1809,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>152</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>204</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>80</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>37</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>11</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-70.270270270270</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-86.25</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-94.607843137254</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-92.763157894736</v>
       </c>
     </row>
@@ -1841,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>44</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>37</v>
       </c>
-      <c r="G42" s="15">
-        <v>21</v>
-      </c>
-      <c r="I42" s="15">
+      <c r="G42" s="14">
+        <v>21</v>
+      </c>
+      <c r="I42" s="14">
         <v>10</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>24</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>140</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>14.285714285714</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-35.135135135135</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-45.454545454545</v>
       </c>
     </row>
@@ -1873,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
-        <v>20</v>
-      </c>
-      <c r="E43" s="15">
+      <c r="C43" s="14">
+        <v>20</v>
+      </c>
+      <c r="E43" s="14">
         <v>34</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>5</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>7</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>2</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-71.428571428571</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-60</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-94.117647058823</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-90</v>
       </c>
     </row>
@@ -1905,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>132</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>176</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>76</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>69</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>45</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-34.782608695652</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-40.789473684210</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-74.431818181818</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-65.909090909090</v>
       </c>
     </row>
@@ -1937,16 +1934,16 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>7</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>11</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>0</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>0</v>
       </c>
       <c r="K45" s="13" t="s">
@@ -1966,66 +1963,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="17">
         <v>368</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="17">
         <v>475</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="17">
         <v>187</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="17">
         <v>127</v>
       </c>
-      <c r="J46" s="18">
+      <c r="J46" s="17">
         <v>85</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="24">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="25">
+      <c r="L46" s="24">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="25">
+      <c r="M46" s="24">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="24">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="25" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="25" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="25" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="25" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="25" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2033,7 +2030,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="27" t="s">
+      <c r="K57" s="26" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -547,6 +547,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -728,24 +731,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="28" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="27"/>
+      <c r="N7" s="28"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -767,45 +770,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="33" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="33" t="s">
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="33" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="33" t="s">
+      <c r="J12" s="33"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="37" t="s">
         <v>16</v>
       </c>
     </row>
@@ -895,8 +898,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -936,8 +939,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,31 +949,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
         <v>1</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J16" s="14">
         <v>2</v>
       </c>
       <c r="K16" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L16" s="15">
-        <v>-76.923076923076</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-40</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.5</v>
+        <v>-80.769230769230</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -990,7 +993,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="15">
         <v>-100</v>
@@ -1005,13 +1008,13 @@
         <v>-75</v>
       </c>
       <c r="L17" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="M17" s="15">
         <v>0</v>
       </c>
-      <c r="M17" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="N17" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1059,23 +1062,23 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
-        <v>1</v>
-      </c>
-      <c r="D19" s="14">
-        <v>1</v>
-      </c>
-      <c r="E19" s="15">
-        <v>0</v>
+      <c r="C19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F19" s="14">
         <v>1</v>
       </c>
       <c r="G19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H19" s="15">
-        <v>-83.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="I19" s="14">
         <v>3</v>
@@ -1090,7 +1093,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="N19" s="15">
         <v>-80</v>
@@ -1144,38 +1147,38 @@
       <c r="C21" s="17">
         <v>2</v>
       </c>
-      <c r="D21" s="17">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18">
-        <v>100</v>
+      <c r="D21" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="F21" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" s="17">
-        <v>9</v>
-      </c>
-      <c r="H21" s="18">
-        <v>-66.666666666666</v>
+        <v>7</v>
+      </c>
+      <c r="H21" s="19">
+        <v>-28.571428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J21" s="17">
         <v>16</v>
       </c>
-      <c r="K21" s="18">
-        <v>-37.5</v>
-      </c>
-      <c r="L21" s="18">
-        <v>-58.333333333333</v>
-      </c>
-      <c r="M21" s="18">
-        <v>-9.090909090909</v>
-      </c>
-      <c r="N21" s="18">
-        <v>-82.142857142857</v>
+      <c r="K21" s="19">
+        <v>-25</v>
+      </c>
+      <c r="L21" s="19">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="M21" s="19">
+        <v>-20</v>
+      </c>
+      <c r="N21" s="19">
+        <v>-80.327868852459</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1264,38 +1267,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="14">
-        <v>2</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>21</v>
+      <c r="C24" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-100</v>
       </c>
       <c r="F24" s="14">
         <v>3</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>21</v>
+      <c r="G24" s="14">
+        <v>1</v>
+      </c>
+      <c r="H24" s="15">
+        <v>200</v>
       </c>
       <c r="I24" s="14">
         <v>5</v>
       </c>
       <c r="J24" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="L24" s="15">
         <v>150</v>
       </c>
       <c r="M24" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1347,7 +1350,7 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>20</v>
@@ -1356,28 +1359,28 @@
         <v>21</v>
       </c>
       <c r="F26" s="14">
-        <v>2</v>
-      </c>
-      <c r="G26" s="14">
-        <v>1</v>
-      </c>
-      <c r="H26" s="15">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J26" s="14">
         <v>3</v>
       </c>
       <c r="K26" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L26" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="M26" s="15">
-        <v>-42.857142857142</v>
+        <v>-40</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1390,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1592,19 +1595,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1651,93 +1654,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="31"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="32"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="20" t="s">
+      <c r="J37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="21" t="s">
+      <c r="L37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="21" t="s">
+      <c r="M37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="21" t="s">
+      <c r="N37" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="23">
         <v>2025</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="21" t="s">
+      <c r="M38" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="21" t="s">
+      <c r="N38" s="22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1978,51 +1981,51 @@
       <c r="J46" s="17">
         <v>85</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="25">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L46" s="25">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="24">
+      <c r="M46" s="25">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="24">
+      <c r="N46" s="25">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="26" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="26" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="26" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2030,7 +2033,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="26" t="s">
+      <c r="K57" s="27" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -546,10 +546,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -698,7 +698,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -901,29 +901,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+      <c r="J15" s="14">
+        <v>1</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -932,30 +932,30 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
-        <v>3</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15">
-        <v>200</v>
+      <c r="G16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
@@ -973,7 +973,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.769230769230</v>
+        <v>-82.758620689655</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -992,11 +992,11 @@
       <c r="F17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="14">
-        <v>1</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-100</v>
+      <c r="G17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I17" s="14">
         <v>1</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-90</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1075,10 +1075,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="I19" s="14">
         <v>3</v>
@@ -1093,10 +1093,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-80</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1144,41 +1144,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17">
-        <v>2</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="18">
+        <v>1</v>
+      </c>
+      <c r="E21" s="19">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="18">
+        <v>4</v>
+      </c>
+      <c r="G21" s="18">
         <v>5</v>
       </c>
-      <c r="G21" s="17">
-        <v>7</v>
-      </c>
       <c r="H21" s="19">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="I21" s="17">
+        <v>-20</v>
+      </c>
+      <c r="I21" s="18">
         <v>12</v>
       </c>
-      <c r="J21" s="17">
-        <v>16</v>
+      <c r="J21" s="18">
+        <v>17</v>
       </c>
       <c r="K21" s="19">
-        <v>-25</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L21" s="19">
         <v>-57.142857142857</v>
       </c>
       <c r="M21" s="19">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="N21" s="19">
-        <v>-80.327868852459</v>
+        <v>-83.561643835616</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1271,7 +1271,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="15">
         <v>-100</v>
@@ -1280,25 +1280,25 @@
         <v>3</v>
       </c>
       <c r="G24" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" s="15">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="14">
         <v>5</v>
       </c>
       <c r="J24" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K24" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="M24" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1335,8 +1335,8 @@
       <c r="K25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L25" s="13" t="s">
-        <v>21</v>
+      <c r="L25" s="15">
+        <v>-100</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1349,8 +1349,8 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>2</v>
+      <c r="C26" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>20</v>
@@ -1393,29 +1393,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>21</v>
+      <c r="J27" s="14">
+        <v>1</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0</v>
       </c>
       <c r="L27" s="15">
         <v>-50</v>
@@ -1966,19 +1966,19 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="18">
         <v>368</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="18">
         <v>475</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="18">
         <v>187</v>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="18">
         <v>127</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="18">
         <v>85</v>
       </c>
       <c r="K46" s="25">

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,9 +544,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -698,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -731,24 +728,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="29" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="28"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -770,45 +767,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="34" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="34" t="s">
+      <c r="G12" s="32"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="34" t="s">
+      <c r="J12" s="32"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="36" t="s">
         <v>16</v>
       </c>
     </row>
@@ -901,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -939,8 +936,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -949,7 +946,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -958,30 +955,30 @@
         <v>21</v>
       </c>
       <c r="I16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="14">
         <v>2</v>
       </c>
       <c r="K16" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L16" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.758620689655</v>
+        <v>-80.645161290322</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>20</v>
@@ -989,8 +986,8 @@
       <c r="E17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>20</v>
+      <c r="F17" s="14">
+        <v>1</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>20</v>
@@ -999,22 +996,22 @@
         <v>21</v>
       </c>
       <c r="I17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="14">
         <v>4</v>
       </c>
       <c r="K17" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L17" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-91.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1062,41 +1059,41 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>21</v>
+      <c r="C19" s="14">
+        <v>2</v>
+      </c>
+      <c r="D19" s="14">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="15">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="I19" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K19" s="15">
-        <v>-70</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L19" s="15">
-        <v>-66.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M19" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="N19" s="15">
-        <v>-84.210526315789</v>
+        <v>-79.166666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1144,41 +1141,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="18">
+      <c r="C21" s="17">
+        <v>4</v>
+      </c>
+      <c r="D21" s="17">
         <v>1</v>
       </c>
-      <c r="E21" s="19">
-        <v>-100</v>
-      </c>
-      <c r="F21" s="18">
-        <v>4</v>
-      </c>
-      <c r="G21" s="18">
-        <v>5</v>
-      </c>
-      <c r="H21" s="19">
-        <v>-20</v>
-      </c>
-      <c r="I21" s="18">
-        <v>12</v>
-      </c>
-      <c r="J21" s="18">
-        <v>17</v>
-      </c>
-      <c r="K21" s="19">
-        <v>-29.411764705882</v>
-      </c>
-      <c r="L21" s="19">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="M21" s="19">
-        <v>-25</v>
-      </c>
-      <c r="N21" s="19">
-        <v>-83.561643835616</v>
+      <c r="E21" s="18">
+        <v>300</v>
+      </c>
+      <c r="F21" s="17">
+        <v>8</v>
+      </c>
+      <c r="G21" s="17">
+        <v>3</v>
+      </c>
+      <c r="H21" s="18">
+        <v>166.666666666667</v>
+      </c>
+      <c r="I21" s="17">
+        <v>16</v>
+      </c>
+      <c r="J21" s="17">
+        <v>18</v>
+      </c>
+      <c r="K21" s="18">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="L21" s="18">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="M21" s="18">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="N21" s="18">
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1270,20 +1267,20 @@
       <c r="C24" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="14">
-        <v>3</v>
-      </c>
-      <c r="E24" s="15">
-        <v>-100</v>
+      <c r="D24" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F24" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="14">
         <v>4</v>
       </c>
       <c r="H24" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I24" s="14">
         <v>5</v>
@@ -1295,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M24" s="15">
         <v>0</v>
@@ -1359,7 +1356,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>20</v>
@@ -1377,7 +1374,7 @@
         <v>100</v>
       </c>
       <c r="L26" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
         <v>-40</v>
@@ -1393,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1431,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1595,19 +1592,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1654,93 +1651,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="K37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="22" t="s">
+      <c r="I38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="22">
         <v>2025</v>
       </c>
-      <c r="K38" s="22" t="s">
+      <c r="K38" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="M38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="22" t="s">
+      <c r="N38" s="21" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1966,66 +1963,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="17">
         <v>368</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="17">
         <v>475</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="17">
         <v>187</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="17">
         <v>127</v>
       </c>
-      <c r="J46" s="18">
+      <c r="J46" s="17">
         <v>85</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="24">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="25">
+      <c r="L46" s="24">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="25">
+      <c r="M46" s="24">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="24">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="25" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="25" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="25" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="25" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="25" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2033,7 +2030,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="27" t="s">
+      <c r="K57" s="26" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +544,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -695,7 +698,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -728,24 +731,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="28" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="27"/>
+      <c r="N7" s="28"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -767,45 +770,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="33" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="33" t="s">
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="33" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="33" t="s">
+      <c r="J12" s="33"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="37" t="s">
         <v>16</v>
       </c>
     </row>
@@ -904,14 +907,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
@@ -925,8 +928,8 @@
       <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="15">
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>-50</v>
@@ -936,8 +939,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -964,45 +967,45 @@
         <v>200</v>
       </c>
       <c r="L16" s="15">
-        <v>-60</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="M16" s="15">
         <v>-14.285714285714</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.645161290322</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="E17" s="15">
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>21</v>
+      <c r="G17" s="14">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15">
+        <v>0</v>
       </c>
       <c r="I17" s="14">
         <v>2</v>
       </c>
       <c r="J17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L17" s="15">
         <v>-33.333333333333</v>
@@ -1011,7 +1014,7 @@
         <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1059,41 +1062,41 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
-        <v>2</v>
+      <c r="C19" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="14">
         <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F19" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="14">
         <v>2</v>
       </c>
       <c r="H19" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
         <v>5</v>
       </c>
       <c r="J19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K19" s="15">
+        <v>-58.333333333333</v>
+      </c>
+      <c r="L19" s="15">
         <v>-54.545454545454</v>
       </c>
-      <c r="L19" s="15">
-        <v>-44.444444444444</v>
-      </c>
       <c r="M19" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N19" s="15">
-        <v>-79.166666666666</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1141,41 +1144,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="18">
+        <v>2</v>
+      </c>
+      <c r="E21" s="19">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="18">
+        <v>6</v>
+      </c>
+      <c r="G21" s="18">
         <v>4</v>
       </c>
-      <c r="D21" s="17">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18">
-        <v>300</v>
-      </c>
-      <c r="F21" s="17">
-        <v>8</v>
-      </c>
-      <c r="G21" s="17">
-        <v>3</v>
-      </c>
-      <c r="H21" s="18">
-        <v>166.666666666667</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="H21" s="19">
+        <v>50</v>
+      </c>
+      <c r="I21" s="18">
         <v>16</v>
       </c>
-      <c r="J21" s="17">
-        <v>18</v>
-      </c>
-      <c r="K21" s="18">
-        <v>-11.111111111111</v>
-      </c>
-      <c r="L21" s="18">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="M21" s="18">
-        <v>-11.111111111111</v>
-      </c>
-      <c r="N21" s="18">
-        <v>-80</v>
+      <c r="J21" s="18">
+        <v>20</v>
+      </c>
+      <c r="K21" s="19">
+        <v>-20</v>
+      </c>
+      <c r="L21" s="19">
+        <v>-50</v>
+      </c>
+      <c r="M21" s="19">
+        <v>-20</v>
+      </c>
+      <c r="N21" s="19">
+        <v>-81.609195402298</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1264,8 +1267,8 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>20</v>
+      <c r="C24" s="14">
+        <v>4</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>20</v>
@@ -1274,28 +1277,28 @@
         <v>21</v>
       </c>
       <c r="F24" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24" s="14">
         <v>4</v>
       </c>
       <c r="H24" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J24" s="14">
         <v>5</v>
       </c>
       <c r="K24" s="15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L24" s="15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M24" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,8 +1308,8 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>20</v>
@@ -1314,8 +1317,8 @@
       <c r="E25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>20</v>
+      <c r="F25" s="14">
+        <v>1</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>20</v>
@@ -1323,8 +1326,8 @@
       <c r="H25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I25" s="13" t="s">
-        <v>20</v>
+      <c r="I25" s="14">
+        <v>1</v>
       </c>
       <c r="J25" s="13" t="s">
         <v>20</v>
@@ -1333,7 +1336,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1349,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+      <c r="C26" s="14">
+        <v>1</v>
+      </c>
+      <c r="D26" s="14">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>3</v>
       </c>
-      <c r="G26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>21</v>
+      <c r="G26" s="14">
+        <v>1</v>
+      </c>
+      <c r="H26" s="15">
+        <v>200</v>
       </c>
       <c r="I26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J26" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,14 +1399,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
@@ -1431,32 +1434,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
         <v>3</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1592,19 +1595,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1651,93 +1654,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="31"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="32"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="20" t="s">
+      <c r="J37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="21" t="s">
+      <c r="L37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="21" t="s">
+      <c r="M37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="21" t="s">
+      <c r="N37" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="23">
         <v>2025</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="21" t="s">
+      <c r="M38" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="21" t="s">
+      <c r="N38" s="22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1963,66 +1966,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="18">
         <v>368</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="18">
         <v>475</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="18">
         <v>187</v>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="18">
         <v>127</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="18">
         <v>85</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="25">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L46" s="25">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="24">
+      <c r="M46" s="25">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="24">
+      <c r="N46" s="25">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="26" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="26" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="26" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2030,7 +2033,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="26" t="s">
+      <c r="K57" s="27" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,9 +544,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -698,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -731,24 +728,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="29" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="28"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -770,45 +767,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="34" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="34" t="s">
+      <c r="G12" s="32"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="34" t="s">
+      <c r="J12" s="32"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="36" t="s">
         <v>16</v>
       </c>
     </row>
@@ -949,7 +946,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>20</v>
@@ -967,13 +964,13 @@
         <v>200</v>
       </c>
       <c r="L16" s="15">
-        <v>-64.705882352941</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="M16" s="15">
         <v>-14.285714285714</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -993,28 +990,28 @@
         <v>1</v>
       </c>
       <c r="G17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="14">
         <v>2</v>
       </c>
       <c r="J17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M17" s="15">
         <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1062,41 +1059,41 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="14">
-        <v>1</v>
-      </c>
-      <c r="E19" s="15">
-        <v>-100</v>
+      <c r="C19" s="14">
+        <v>2</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="14">
         <v>2</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J19" s="14">
         <v>12</v>
       </c>
       <c r="K19" s="15">
-        <v>-58.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-54.545454545454</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-54.545454545454</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N19" s="15">
-        <v>-80</v>
+        <v>-78.787878787878</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1144,41 +1141,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="18">
+      <c r="C21" s="17">
         <v>2</v>
       </c>
-      <c r="E21" s="19">
-        <v>-100</v>
-      </c>
-      <c r="F21" s="18">
+      <c r="D21" s="17">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18">
+        <v>100</v>
+      </c>
+      <c r="F21" s="17">
         <v>6</v>
       </c>
-      <c r="G21" s="18">
-        <v>4</v>
-      </c>
-      <c r="H21" s="19">
-        <v>50</v>
-      </c>
-      <c r="I21" s="18">
-        <v>16</v>
-      </c>
-      <c r="J21" s="18">
-        <v>20</v>
-      </c>
-      <c r="K21" s="19">
-        <v>-20</v>
-      </c>
-      <c r="L21" s="19">
+      <c r="G21" s="17">
+        <v>5</v>
+      </c>
+      <c r="H21" s="18">
+        <v>20</v>
+      </c>
+      <c r="I21" s="17">
+        <v>18</v>
+      </c>
+      <c r="J21" s="17">
+        <v>21</v>
+      </c>
+      <c r="K21" s="18">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="L21" s="18">
         <v>-50</v>
       </c>
-      <c r="M21" s="19">
-        <v>-20</v>
-      </c>
-      <c r="N21" s="19">
-        <v>-81.609195402298</v>
+      <c r="M21" s="18">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="N21" s="18">
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1267,8 +1264,8 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="14">
-        <v>4</v>
+      <c r="C24" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>20</v>
@@ -1280,10 +1277,10 @@
         <v>4</v>
       </c>
       <c r="G24" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I24" s="14">
         <v>9</v>
@@ -1308,8 +1305,8 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>20</v>
@@ -1352,11 +1349,11 @@
       <c r="C26" s="14">
         <v>1</v>
       </c>
-      <c r="D26" s="14">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15">
-        <v>0</v>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="14">
         <v>3</v>
@@ -1368,19 +1365,19 @@
         <v>200</v>
       </c>
       <c r="I26" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J26" s="14">
         <v>4</v>
       </c>
       <c r="K26" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="L26" s="15">
-        <v>16.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M26" s="15">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,32 +1428,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="15">
         <v>300</v>
@@ -1595,19 +1592,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1654,93 +1651,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="K37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="22" t="s">
+      <c r="I38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="22">
         <v>2025</v>
       </c>
-      <c r="K38" s="22" t="s">
+      <c r="K38" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="M38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="22" t="s">
+      <c r="N38" s="21" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1966,66 +1963,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="17">
         <v>368</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="17">
         <v>475</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="17">
         <v>187</v>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="17">
         <v>127</v>
       </c>
-      <c r="J46" s="18">
+      <c r="J46" s="17">
         <v>85</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="24">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="25">
+      <c r="L46" s="24">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="25">
+      <c r="M46" s="24">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="24">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="25" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="25" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="25" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="25" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="25" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2033,7 +2030,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="27" t="s">
+      <c r="K57" s="26" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-022pct.xlsx
+++ b/data/source/weekly/cs-en-us-022pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +544,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -695,10 +698,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.699091" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -728,24 +731,24 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="28" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="27"/>
+      <c r="N7" s="28"/>
     </row>
     <row r="8" spans="1:13" customHeight="1" ht="31.500000">
       <c r="A8" s="2" t="s">
@@ -767,45 +770,45 @@
       <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="33" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="33" t="s">
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="33" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="33" t="s">
+      <c r="J12" s="33"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="37" t="s">
         <v>16</v>
       </c>
     </row>
@@ -907,11 +910,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
@@ -967,10 +970,10 @@
         <v>-68.421052631578</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -980,11 +983,11 @@
       <c r="C17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="14">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>-100</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
         <v>1</v>
@@ -1011,7 +1014,7 @@
         <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1048,8 +1051,8 @@
       <c r="L18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="13" t="s">
-        <v>21</v>
+      <c r="M18" s="15">
+        <v>-100</v>
       </c>
       <c r="N18" s="15">
         <v>-100</v>
@@ -1059,41 +1062,41 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
         <v>2</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>21</v>
+      <c r="E19" s="15">
+        <v>-100</v>
       </c>
       <c r="F19" s="14">
         <v>4</v>
       </c>
       <c r="G19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
         <v>7</v>
       </c>
       <c r="J19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K19" s="15">
-        <v>-41.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L19" s="15">
         <v>-41.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="N19" s="15">
-        <v>-78.787878787878</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1141,41 +1144,41 @@
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="18">
         <v>2</v>
       </c>
-      <c r="D21" s="17">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18">
-        <v>100</v>
-      </c>
-      <c r="F21" s="17">
+      <c r="E21" s="19">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="18">
         <v>6</v>
       </c>
-      <c r="G21" s="17">
-        <v>5</v>
-      </c>
-      <c r="H21" s="18">
-        <v>20</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="G21" s="18">
+        <v>6</v>
+      </c>
+      <c r="H21" s="19">
+        <v>0</v>
+      </c>
+      <c r="I21" s="18">
         <v>18</v>
       </c>
-      <c r="J21" s="17">
-        <v>21</v>
-      </c>
-      <c r="K21" s="18">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="L21" s="18">
+      <c r="J21" s="18">
+        <v>23</v>
+      </c>
+      <c r="K21" s="19">
+        <v>-21.739130434782</v>
+      </c>
+      <c r="L21" s="19">
         <v>-50</v>
       </c>
-      <c r="M21" s="18">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="N21" s="18">
-        <v>-82.352941176470</v>
+      <c r="M21" s="19">
+        <v>-28</v>
+      </c>
+      <c r="N21" s="19">
+        <v>-83.928571428571</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1264,38 +1267,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>21</v>
+      <c r="C24" s="14">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15">
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="15">
-        <v>33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="I24" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J24" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K24" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L24" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1333,7 +1336,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1349,35 +1352,35 @@
       <c r="C26" s="14">
         <v>1</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+      <c r="D26" s="14">
+        <v>2</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
+        <v>4</v>
+      </c>
+      <c r="G26" s="14">
         <v>3</v>
       </c>
-      <c r="G26" s="14">
-        <v>1</v>
-      </c>
       <c r="H26" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K26" s="15">
-        <v>125</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M26" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1399,11 +1402,11 @@
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
@@ -1431,11 +1434,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1456,7 +1459,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,8 +1563,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1569,8 +1572,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1592,19 +1595,19 @@
       <c r="A32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="13" t="s">
@@ -1651,93 +1654,93 @@
       <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="31"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="32"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="20" t="s">
+      <c r="J37" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="21" t="s">
+      <c r="L37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="21" t="s">
+      <c r="M37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="21" t="s">
+      <c r="N37" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="23">
         <v>2025</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M38" s="21" t="s">
+      <c r="M38" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N38" s="21" t="s">
+      <c r="N38" s="22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1963,66 +1966,66 @@
       <c r="A46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="18">
         <v>368</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="18">
         <v>475</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="18">
         <v>187</v>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="18">
         <v>127</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="18">
         <v>85</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="25">
         <v>-33.070866141732</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L46" s="25">
         <v>-54.545454545454</v>
       </c>
-      <c r="M46" s="24">
+      <c r="M46" s="25">
         <v>-82.105263157894</v>
       </c>
-      <c r="N46" s="24">
+      <c r="N46" s="25">
         <v>-76.902173913043</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="26" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="26" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="26" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2030,7 +2033,7 @@
       <c r="A57" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K57" s="26" t="s">
+      <c r="K57" s="27" t="s">
         <v>7</v>
       </c>
     </row>
